--- a/ToxCast_model/experiments/prediction/KGML/KGML4Gapfilling_prediction.xlsx
+++ b/ToxCast_model/experiments/prediction/KGML/KGML4Gapfilling_prediction.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="data"/>
@@ -1152,7 +1152,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1586,8 +1586,8 @@
   <dimension ref="A1:BN147"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="20.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="54.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="20.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="54.29071428571429" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="10" width="13.005" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="10" width="13.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="10" width="13.005" customWidth="1" bestFit="1"/>
@@ -1654,7 +1654,7 @@
     <col min="66" max="66" style="10" width="13.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21">
       <c r="A1" s="5" t="s">
         <v>78</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="8" t="s">
         <v>80</v>
       </c>
@@ -1926,7 +1926,7 @@
       <c r="BM2" s="9"/>
       <c r="BN2" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="8" t="s">
         <v>82</v>
       </c>
@@ -1998,7 +1998,7 @@
       <c r="BM3" s="9"/>
       <c r="BN3" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="8" t="s">
         <v>84</v>
       </c>
@@ -2070,7 +2070,7 @@
       <c r="BM4" s="9"/>
       <c r="BN4" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="8" t="s">
         <v>86</v>
       </c>
@@ -2142,7 +2142,7 @@
       <c r="BM5" s="9"/>
       <c r="BN5" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="8" t="s">
         <v>88</v>
       </c>
@@ -2214,7 +2214,7 @@
       <c r="BM6" s="9"/>
       <c r="BN6" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="8" t="s">
         <v>90</v>
       </c>
@@ -2286,7 +2286,7 @@
       <c r="BM7" s="9"/>
       <c r="BN7" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="8" t="s">
         <v>92</v>
       </c>
@@ -2358,7 +2358,7 @@
       <c r="BM8" s="9"/>
       <c r="BN8" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="8" t="s">
         <v>94</v>
       </c>
@@ -2430,7 +2430,7 @@
       <c r="BM9" s="9"/>
       <c r="BN9" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="8" t="s">
         <v>96</v>
       </c>
@@ -2502,7 +2502,7 @@
       <c r="BM10" s="9"/>
       <c r="BN10" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="8" t="s">
         <v>98</v>
       </c>
@@ -2574,7 +2574,7 @@
       <c r="BM11" s="9"/>
       <c r="BN11" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="8" t="s">
         <v>100</v>
       </c>
@@ -2646,7 +2646,7 @@
       <c r="BM12" s="9"/>
       <c r="BN12" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="8" t="s">
         <v>102</v>
       </c>
@@ -2718,7 +2718,7 @@
       <c r="BM13" s="9"/>
       <c r="BN13" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="8" t="s">
         <v>104</v>
       </c>
